--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="M2">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -684,7 +684,7 @@
         <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S2">
         <v>2.45</v>
@@ -708,31 +708,31 @@
         <v>6.5</v>
       </c>
       <c r="Z2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA2">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
         <v>2.4</v>
       </c>
       <c r="AG2">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH2">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI2">
         <v>1.04</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -684,10 +684,10 @@
         <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T2">
         <v>3.5</v>
@@ -699,31 +699,31 @@
         <v>11</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="Z2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB2">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>2.4</v>
@@ -732,7 +732,7 @@
         <v>1.53</v>
       </c>
       <c r="AH2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AI2">
         <v>1.04</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>5.94</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -687,7 +687,7 @@
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T2">
         <v>3.5</v>
@@ -699,13 +699,13 @@
         <v>11</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="Z2">
         <v>1.5</v>
@@ -714,7 +714,7 @@
         <v>2.5</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
@@ -723,7 +723,7 @@
         <v>4.75</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
         <v>2.4</v>
@@ -732,7 +732,7 @@
         <v>1.53</v>
       </c>
       <c r="AH2">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AI2">
         <v>1.04</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="N2">
-        <v>5.94</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -687,34 +687,34 @@
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
         <v>1.29</v>
       </c>
       <c r="V2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Z2">
         <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB2">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
@@ -723,7 +723,7 @@
         <v>4.75</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
         <v>2.4</v>
@@ -732,10 +732,10 @@
         <v>1.53</v>
       </c>
       <c r="AH2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI2">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="s">
         <v>44</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="M2">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>5.92</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -687,40 +687,40 @@
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="Z2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA2">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AE2">
         <v>1.15</v>
@@ -732,10 +732,10 @@
         <v>1.53</v>
       </c>
       <c r="AH2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
         <v>44</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -666,13 +666,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="N2">
-        <v>5.92</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -684,46 +684,46 @@
         <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S2">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="T2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V2">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W2">
         <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AB2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>2.4</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -145,10 +145,13 @@
     <t>Amazonas</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
-    <t>[]</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['74', '29', '35']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -651,28 +654,28 @@
         <v>42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -684,64 +687,64 @@
         <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S2">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="V2">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y2">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="Z2">
+        <v>1.6</v>
+      </c>
+      <c r="AA2">
+        <v>2.24</v>
+      </c>
+      <c r="AB2">
+        <v>2.7</v>
+      </c>
+      <c r="AC2">
+        <v>1.49</v>
+      </c>
+      <c r="AD2">
+        <v>5.75</v>
+      </c>
+      <c r="AE2">
+        <v>1.15</v>
+      </c>
+      <c r="AF2">
+        <v>2.5</v>
+      </c>
+      <c r="AG2">
         <v>1.5</v>
-      </c>
-      <c r="AA2">
-        <v>2.59</v>
-      </c>
-      <c r="AB2">
-        <v>2.3</v>
-      </c>
-      <c r="AC2">
-        <v>1.5</v>
-      </c>
-      <c r="AD2">
-        <v>5.5</v>
-      </c>
-      <c r="AE2">
-        <v>1.17</v>
-      </c>
-      <c r="AF2">
-        <v>2.4</v>
-      </c>
-      <c r="AG2">
-        <v>1.53</v>
       </c>
       <c r="AH2">
         <v>11</v>
       </c>
       <c r="AI2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="s">
         <v>44</v>
       </c>
       <c r="AK2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AL2" s="3">
         <v>45853.8125</v>

--- a/jogos_2025-07-15.xlsx
+++ b/jogos_2025-07-15.xlsx
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,31 +927,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
         <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
         <v>1.57</v>
@@ -960,10 +960,10 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.55</v>
@@ -972,38 +972,38 @@
         <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['55', '60', '89']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45853.58333333334</v>
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Milsami</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['55', '60', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.7</v>
+        <v>1.61</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45853.58333333334</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Milsami</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.85</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.35</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>3.64</v>
+        <v>4.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.55</v>
+        <v>1.34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.61</v>
+        <v>3.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45853.58333333334</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,43 +1830,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>4.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
         <v>1.85</v>
@@ -1875,38 +1875,38 @@
         <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['68', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['6', '29']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['15', '23', '27', '38', '69']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45853.66666666666</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Virtus</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.1</v>
+        <v>1.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>36</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.63</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>3.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>1.69</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>2.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['68', '90+1']</t>
+          <t>['40', '75']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['6', '29']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45853.66666666666</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Virtus</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.05</v>
+        <v>2.03</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>36</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.48</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['40', '75']</t>
+          <t>['15', '23', '27', '38', '69']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>15</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45853.66666666666</v>
